--- a/karkard/output/کارکرد-مهر-1405.xlsx
+++ b/karkard/output/کارکرد-مهر-1405.xlsx
@@ -802,12 +802,12 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۴۵</t>
+          <t>۰۸:۵۵</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>۱۶:۲۵</t>
+          <t>۱۷:۳۵</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -821,7 +821,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="25" customHeight="1">
+    <row r="7" ht="28" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>۲</t>
@@ -834,12 +834,12 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۳۰</t>
+          <t>۰۸:۲۰</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>۱۱:۱۵</t>
+          <t>۱۲:۰۵</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام و پاسخگویی به سؤالات نواحی؛ دریافت و دسته‌بندی گزارش‌های ماهانه نواحی برای تهیه کارنامه عملکرد؛ بررسی گزارش‌های ارسالی ناحیه خور و بیابانک و رفع اشکال موارد ناقص</t>
+          <t>به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام و پاسخگویی به سؤالات نواحی؛ دریافت و دسته‌بندی گزارش‌های ماهانه نواحی برای تهیه کارنامه عملکرد؛ بررسی گزارش‌های ارسالی ناحیه خور و بیابانک و رفع اشکال موارد ناقص؛ تجمیع و تکمیل گزارش کارکرد ماه شهریور</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۲۵</t>
+          <t>۰۸:۱۵</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>۱۵:۳۰</t>
+          <t>۱۶:۲۰</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>۰۸:۰۰</t>
+          <t>۰۹:۲۵</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>۱۶:۲۰</t>
+          <t>۱۷:۴۵</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -950,12 +950,12 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۵۵</t>
+          <t>۰۹:۱۵</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۰۰</t>
+          <t>۱۸:۲۰</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۲۰</t>
+          <t>۰۸:۰۰</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>۱۶:۲۵</t>
+          <t>۱۷:۰۵</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۵۵</t>
+          <t>۰۹:۱۵</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>۱۶:۰۵</t>
+          <t>۱۷:۲۵</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۵۰</t>
+          <t>۰۹:۰۵</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>۱۱:۴۰</t>
+          <t>۱۲:۵۵</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
+    <row r="15" ht="25" customHeight="1">
       <c r="A15" s="17" t="inlineStr">
         <is>
           <t>۱۰</t>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>۰۹:۴۵</t>
+          <t>۰۸:۴۵</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>۱۱:۰۰</t>
+          <t>۱۰:۰۰</t>
         </is>
       </c>
       <c r="E15" s="18" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>جمعه (تعطیل هفتگی) ـ ارتباط با مسئولان فضای مجازی نواحی و هماهنگی انتشار محتوای مناسبتی (دورکاری)</t>
+          <t>جمعه (تعطیل هفتگی) ـ ارتباط با مسئولان فضای مجازی نواحی و هماهنگی انتشار محتوای مناسبتی؛ انتشار محتوای مناسبتی در کانال‌های استانی و پاسخگویی به مخاطبان (دورکاری)</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۳۰</t>
+          <t>۰۸:۲۰</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>۱۵:۴۰</t>
+          <t>۱۶:۳۰</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۳۵</t>
+          <t>۰۸:۳۰</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>۱۶:۱۰</t>
+          <t>۱۷:۰۵</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۲۵</t>
+          <t>۰۸:۱۵</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>۱۶:۵۰</t>
+          <t>۱۷:۴۰</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۳۵</t>
+          <t>۰۸:۳۰</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>۱۷:۰۵</t>
+          <t>۱۸:۰۰</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>۰۸:۱۰</t>
+          <t>۰۹:۰۰</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>۱۶:۵۰</t>
+          <t>۱۷:۴۰</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۵۰</t>
+          <t>۰۹:۳۰</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>۱۱:۲۵</t>
+          <t>۱۳:۰۵</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>۰۸:۰۵</t>
+          <t>۰۹:۰۵</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۱۰</t>
+          <t>۱۸:۱۰</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۵۰</t>
+          <t>۰۸:۴۵</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>۱۶:۴۵</t>
+          <t>۱۷:۴۰</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۴۰</t>
+          <t>۰۸:۵۵</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>۱۶:۰۰</t>
+          <t>۱۷:۱۵</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>۰۸:۱۰</t>
+          <t>۰۸:۰۵</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>۱۷:۲۰</t>
+          <t>۱۷:۱۵</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۴۵</t>
+          <t>۰۸:۱۰</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۲۰</t>
+          <t>۱۷:۴۵</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۲۰</t>
+          <t>۰۸:۳۰</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>۱۱:۴۰</t>
+          <t>۱۲:۵۰</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۲۵</t>
+          <t>۰۹:۱۰</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>۱۶:۲۰</t>
+          <t>۱۸:۰۵</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۳۵</t>
+          <t>۰۹:۰۰</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>۱۶:۰۰</t>
+          <t>۱۷:۲۵</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۵۵</t>
+          <t>۰۸:۱۵</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>۱۵:۵۵</t>
+          <t>۱۶:۱۵</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>۰۷:۵۰</t>
+          <t>۰۹:۰۵</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>۱۵:۴۵</t>
+          <t>۱۷:۰۰</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>۰۸:۱۰</t>
+          <t>۰۹:۰۵</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۱۰</t>
+          <t>۱۸:۰۵</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>۰۷:۲۵</t>
+          <t>۰۸:۵۰</t>
         </is>
       </c>
       <c r="D35" s="21" t="inlineStr">
         <is>
-          <t>۱۱:۴۵</t>
+          <t>۱۳:۱۰</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">

--- a/karkard/output/کارکرد-مهر-1405.xlsx
+++ b/karkard/output/کارکرد-مهر-1405.xlsx
@@ -1777,7 +1777,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.18" right="0.18" top="0.2" bottom="0.2" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;9 کارکرد مهر ۱۴۰۵ ـ صفحه &amp;P از &amp;N</oddFooter>

--- a/karkard/output/کارکرد-مهر-1405.xlsx
+++ b/karkard/output/کارکرد-مهر-1405.xlsx
@@ -73,7 +73,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -102,11 +102,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF4EA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
@@ -263,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -313,15 +308,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -331,7 +317,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -807,21 +793,21 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۳۵</t>
+          <t>۱۷:۴۰</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>۸:۴۰</t>
+          <t>۸:۴۵</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>پاسخگویی به سؤالات و درخواست‌های نواحی و به‌روزرسانی محتوای کانال‌ها در ایتا، روبیکا و تلگرام؛ جمع‌آوری گزارش کارکرد ماه گذشته از نواحی و بررسی اولیه؛ رصد بازخورد مخاطبان نسبت به محتوای منتشرشده و ثبت پیشنهادها؛ تولید محتوای آموزشی ویژه ناحیه فریدون شهر بر اساس نیاز اعلامی</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
+          <t>پاسخگویی به سؤالات و درخواست‌های نواحی و به‌روزرسانی محتوای کانال‌ها در ایتا، روبیکا و تلگرام؛ جمع‌آوری گزارش کارکرد ماه گذشته از نواحی و بررسی اولیه؛ رصد بازخورد مخاطبان نسبت به محتوای منتشرشده و ثبت پیشنهادها؛ تولید محتوای آموزشی ویژه ناحیه امام علی (ع) بر اساس نیاز اعلامی</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>۲</t>
@@ -839,17 +825,17 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>۱۲:۰۵</t>
+          <t>۱۲:۱۰</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>۳:۴۵</t>
+          <t>۳:۵۰</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام و پاسخگویی به سؤالات نواحی؛ دریافت و دسته‌بندی گزارش‌های ماهانه نواحی برای تهیه کارنامه عملکرد؛ بررسی گزارش‌های ارسالی ناحیه خور و بیابانک و رفع اشکال موارد ناقص؛ تجمیع و تکمیل گزارش کارکرد ماه شهریور</t>
+          <t>به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام و پاسخگویی به سؤالات نواحی؛ دریافت و دسته‌بندی گزارش‌های ماهانه نواحی برای تهیه کارنامه عملکرد؛ بررسی گزارش‌های ارسالی ناحیه لنجان و رفع اشکال موارد ناقص</t>
         </is>
       </c>
     </row>
@@ -869,7 +855,7 @@
       <c r="E8" s="15" t="inlineStr"/>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>جمعه (تعطیل هفتگی)</t>
+          <t>جمعه (تعطیل هفتگی ـ روز ۳ مهر)</t>
         </is>
       </c>
     </row>
@@ -901,7 +887,7 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>رصد و به‌روزرسانی روزانه کانال‌های ایتا، روبیکا و تلگرام و پیگیری پیام‌های نواحی؛ پیگیری ارسال گزارش عملکرد ماه قبل از نواحی باقی‌مانده؛ رصد عملکرد کانال‌های ناحیه تیران و کرون و مقایسه با میانگین استانی؛ تولید محتوای گرافیکی و پوستر سواد رسانه‌ای</t>
+          <t>رصد و به‌روزرسانی روزانه کانال‌های ایتا، روبیکا و تلگرام و پیگیری پیام‌های نواحی؛ پیگیری ارسال گزارش عملکرد ماه قبل از نواحی باقی‌مانده؛ رصد عملکرد کانال‌های ناحیه برخوار و مقایسه با میانگین استانی؛ تولید محتوای گرافیکی و پوستر سواد رسانه‌ای</t>
         </is>
       </c>
     </row>
@@ -923,12 +909,12 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>۱۷:۴۵</t>
+          <t>۱۷:۵۰</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>۸:۲۰</t>
+          <t>۸:۲۵</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
@@ -965,11 +951,11 @@
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>پاسخگویی به سؤالات و درخواست‌های نواحی و به‌روزرسانی محتوای کانال‌ها در ایتا، روبیکا و تلگرام؛ مرتب‌سازی محتوای آموزشی کانال و دسته‌بندی آرشیو انتشار؛ هماهنگی برگزاری کارگاه آموزشی ویژه فعالان رسانه‌ای ناحیه برخوار</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="25" customHeight="1">
+          <t>پاسخگویی به سؤالات و درخواست‌های نواحی و به‌روزرسانی محتوای کانال‌ها در ایتا، روبیکا و تلگرام؛ مرتب‌سازی محتوای آموزشی کانال و دسته‌بندی آرشیو انتشار؛ هماهنگی برگزاری کارگاه آموزشی ویژه فعالان رسانه‌ای ناحیه امام حسین (ع)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>۷</t>
@@ -997,7 +983,7 @@
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام و پاسخگویی به سؤالات نواحی؛ تماس با ناحیه جرقویه و دریافت اطلاعات لازم برای برنامه‌ریزی دوره آموزشی؛ پیگیری تشکیل و فعال‌سازی تیم تولید محتوای ناحیه هرند</t>
+          <t>به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام و پاسخگویی به سؤالات نواحی؛ تماس با ناحیه نطنز و دریافت اطلاعات لازم برای برنامه‌ریزی دوره آموزشی؛ پیگیری تشکیل و فعال‌سازی تیم تولید محتوای ناحیه هرند؛ تجمیع و تکمیل گزارش کارکرد ماه شهریور</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1005,12 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۲۵</t>
+          <t>۱۷:۳۰</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>۸:۱۰</t>
+          <t>۸:۱۵</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
@@ -1051,12 +1037,12 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>۱۲:۵۵</t>
+          <t>۱۳:۰۰</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>۳:۵۰</t>
+          <t>۳:۵۵</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
@@ -1065,35 +1051,23 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>۱۰</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>جمعه</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>۰۸:۴۵</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>۱۰:۰۰</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>۱:۱۵</t>
-        </is>
-      </c>
-      <c r="F15" s="19" t="inlineStr">
-        <is>
-          <t>جمعه (تعطیل هفتگی) ـ ارتباط با مسئولان فضای مجازی نواحی و هماهنگی انتشار محتوای مناسبتی؛ انتشار محتوای مناسبتی در کانال‌های استانی و پاسخگویی به مخاطبان (دورکاری)</t>
+      <c r="C15" s="15" t="inlineStr"/>
+      <c r="D15" s="15" t="inlineStr"/>
+      <c r="E15" s="15" t="inlineStr"/>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>جمعه (تعطیل هفتگی ـ روز ۱۰ مهر)</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1089,17 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>۱۶:۳۰</t>
+          <t>۱۶:۳۵</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>۸:۱۰</t>
+          <t>۸:۱۵</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>پاسخگویی به سؤالات و درخواست‌های نواحی و به‌روزرسانی محتوای کانال‌ها در ایتا، روبیکا و تلگرام؛ پیگیری روند ثبت‌نام و برگزاری کلاس‌های سواد رسانه‌ای ناحیه درچه؛ تدوین سناریوی موشن‌گرافیک آموزشی با موضوع سواد رسانه‌ای</t>
+          <t>پاسخگویی به سؤالات و درخواست‌های نواحی و به‌روزرسانی محتوای کانال‌ها در ایتا، روبیکا و تلگرام؛ پیگیری روند ثبت‌نام و برگزاری کلاس‌های سواد رسانه‌ای ناحیه فریدون شهر؛ تدوین سناریوی موشن‌گرافیک آموزشی با موضوع سواد رسانه‌ای</t>
         </is>
       </c>
     </row>
@@ -1179,17 +1153,17 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۴۰</t>
+          <t>۱۷:۴۵</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>۹:۲۵</t>
+          <t>۹:۳۰</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>رصد و به‌روزرسانی روزانه کانال‌های ایتا، روبیکا و تلگرام و پیگیری پیام‌های نواحی؛ بارگذاری و انتشار پوسترها و کلیپ‌های جدید در کانال‌های استانی؛ رصد و پایش فعالیت‌های فضای مجازی ناحیه نجف آباد و ثبت گزارش روزانه</t>
+          <t>رصد و به‌روزرسانی روزانه کانال‌های ایتا، روبیکا و تلگرام و پیگیری پیام‌های نواحی؛ بارگذاری و انتشار پوسترها و کلیپ‌های جدید در کانال‌های استانی؛ رصد و پایش فعالیت‌های فضای مجازی ناحیه خور و بیابانک و ثبت گزارش روزانه</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1279,7 @@
       <c r="E22" s="15" t="inlineStr"/>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>جمعه (تعطیل هفتگی)</t>
+          <t>جمعه (تعطیل هفتگی ـ روز ۱۷ مهر)</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1333,12 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>۱۷:۴۰</t>
+          <t>۱۷:۴۵</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>۸:۵۵</t>
+          <t>۹:۰۰</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
@@ -1373,7 +1347,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
+    <row r="25" ht="25" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>۲۰</t>
@@ -1391,17 +1365,17 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۱۵</t>
+          <t>۱۷:۲۰</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>۸:۲۰</t>
+          <t>۸:۲۵</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>پاسخگویی به سؤالات و درخواست‌های نواحی و به‌روزرسانی محتوای کانال‌ها در ایتا، روبیکا و تلگرام؛ ارتباط با مسئول نسرا در ناحیه امام صادق (ع) و پیگیری روند اجرای برنامه‌های آموزشی؛ تولید پادکست کوتاه آموزشی با موضوع امنیت در فضای مجازی</t>
+          <t>پاسخگویی به سؤالات و درخواست‌های نواحی و به‌روزرسانی محتوای کانال‌ها در ایتا، روبیکا و تلگرام؛ ارتباط با مسئول نسرا در ناحیه کاشان و پیگیری روند اجرای برنامه‌های آموزشی؛ تولید پادکست کوتاه آموزشی با موضوع امنیت در فضای مجازی</t>
         </is>
       </c>
     </row>
@@ -1455,17 +1429,17 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۴۵</t>
+          <t>۱۷:۵۰</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>۹:۳۵</t>
+          <t>۹:۴۰</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>رصد و به‌روزرسانی روزانه کانال‌های ایتا، روبیکا و تلگرام و پیگیری پیام‌های نواحی؛ انتشار اطلاعیه دوره‌های آموزشی و ثبت‌نام کلاس‌های سواد رسانه‌ای؛ به‌روزرسانی بخش سنجاق‌شده کانال و انتشار اطلاعیه‌های جدید ناحیه کاشان</t>
+          <t>رصد و به‌روزرسانی روزانه کانال‌های ایتا، روبیکا و تلگرام و پیگیری پیام‌های نواحی؛ انتشار اطلاعیه دوره‌های آموزشی و ثبت‌نام کلاس‌های سواد رسانه‌ای؛ به‌روزرسانی بخش سنجاق‌شده کانال و انتشار اطلاعیه‌های جدید ناحیه نجف آباد</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1491,7 @@
       <c r="E29" s="15" t="inlineStr"/>
       <c r="F29" s="16" t="inlineStr">
         <is>
-          <t>جمعه (تعطیل هفتگی)</t>
+          <t>جمعه (تعطیل هفتگی ـ روز ۲۴ مهر)</t>
         </is>
       </c>
     </row>
@@ -1539,17 +1513,17 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>۱۸:۰۵</t>
+          <t>۱۸:۱۰</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>۸:۵۵</t>
+          <t>۹:۰۰</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>پاسخگویی به سؤالات و درخواست‌های نواحی و به‌روزرسانی محتوای کانال‌ها در ایتا، روبیکا و تلگرام؛ طراحی پوستر و اینفوگرافیک آموزشی برای انتشار در کانال استان؛ هماهنگی با مسئول فضای مجازی ناحیه شهرضا برای برنامه‌ریزی اقدامات ماه آینده</t>
+          <t>پاسخگویی به سؤالات و درخواست‌های نواحی و به‌روزرسانی محتوای کانال‌ها در ایتا، روبیکا و تلگرام؛ طراحی پوستر و اینفوگرافیک آموزشی برای انتشار در کانال استان؛ هماهنگی با مسئول فضای مجازی ناحیه درچه برای برنامه‌ریزی اقدامات ماه آینده</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1555,7 @@
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام و پاسخگویی به سؤالات نواحی؛ هماهنگی با فعالان رسانه‌ای ناحیه مبارکه برای توسعه تیم تولید محتوا؛ برگزاری جلسه هماهنگی مجازی با رابطان سواد رسانه‌ای نواحی</t>
+          <t>به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام و پاسخگویی به سؤالات نواحی؛ هماهنگی با فعالان رسانه‌ای ناحیه بویین و میاندشت برای توسعه تیم تولید محتوا؛ برگزاری جلسه هماهنگی مجازی با رابطان سواد رسانه‌ای نواحی</t>
         </is>
       </c>
     </row>
@@ -1603,12 +1577,12 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>۱۶:۱۵</t>
+          <t>۱۶:۲۵</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>۸:۰۰</t>
+          <t>۸:۱۰</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
@@ -1635,12 +1609,12 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>۱۷:۰۰</t>
+          <t>۱۷:۰۵</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>۷:۵۵</t>
+          <t>۸:۰۰</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
@@ -1667,12 +1641,12 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>۱۸:۰۵</t>
+          <t>۱۸:۱۰</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>۹:۰۰</t>
+          <t>۹:۰۵</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
@@ -1682,69 +1656,69 @@
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>۳۰</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="18" t="inlineStr">
         <is>
           <t>پنجشنبه</t>
         </is>
       </c>
-      <c r="C35" s="21" t="inlineStr">
+      <c r="C35" s="18" t="inlineStr">
         <is>
           <t>۰۸:۵۰</t>
         </is>
       </c>
-      <c r="D35" s="21" t="inlineStr">
+      <c r="D35" s="18" t="inlineStr">
         <is>
           <t>۱۳:۱۰</t>
         </is>
       </c>
-      <c r="E35" s="21" t="inlineStr">
+      <c r="E35" s="18" t="inlineStr">
         <is>
           <t>۴:۲۰</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="19" t="inlineStr">
         <is>
           <t>به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام و پاسخگویی به سؤالات نواحی؛ جمع‌بندی گزارش‌های ماه جاری و صدور کارنامه عملکرد نواحی؛ ارزیابی عملکرد ماهانه رابطان سواد رسانه‌ای و ثبت بازخورد</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="23" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>جمع ساعات کارکرد در ماه: ۲۰۴ ساعت و ۱۰ دقیقه</t>
         </is>
       </c>
-      <c r="B36" s="23" t="n"/>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="23" t="n"/>
-      <c r="E36" s="23" t="n"/>
-      <c r="F36" s="23" t="n"/>
+      <c r="B36" s="20" t="n"/>
+      <c r="C36" s="20" t="n"/>
+      <c r="D36" s="20" t="n"/>
+      <c r="E36" s="20" t="n"/>
+      <c r="F36" s="20" t="n"/>
     </row>
     <row r="37" ht="4" customHeight="1"/>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="24" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>امضاء فرد</t>
         </is>
       </c>
-      <c r="B38" s="24" t="n"/>
-      <c r="C38" s="24" t="inlineStr">
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>امضاء مسئول مرکز فضای مجازی</t>
         </is>
       </c>
-      <c r="D38" s="24" t="n"/>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="D38" s="21" t="n"/>
+      <c r="E38" s="21" t="inlineStr">
         <is>
           <t>تأیید مرکز فضای مجازی بسیج استان</t>
         </is>
       </c>
-      <c r="F38" s="24" t="n"/>
+      <c r="F38" s="21" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="4" t="n"/>
